--- a/NEO_TEMPLATE.xlsx
+++ b/NEO_TEMPLATE.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="lapHgcg1OfIb2giMB+1dN8AKkyTggiZxqi5udIUMkIQ="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="TLFuOAxGfz+K6WtGM5ZMEfL3t5CawVupl8Aru4zAkpI="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="76">
   <si>
     <t>channel</t>
   </si>
@@ -72,97 +72,160 @@
     <t>ru</t>
   </si>
   <si>
-    <t>AI trends 2026</t>
-  </si>
-  <si>
-    <t>AI trends, artificial intelligence, future technology, machine learning</t>
-  </si>
-  <si>
     <t>approval</t>
   </si>
   <si>
-    <t>The Future of Remote Work in 2026</t>
+    <t>How to Improve Your Sleep Quality</t>
   </si>
   <si>
-    <t>remote work, work from home, digital nomads, productivity</t>
-  </si>
-  <si>
-    <t>Simple Habits for a Healthy Lifestyle</t>
-  </si>
-  <si>
-    <t>health, habits, lifestyle, wellness</t>
+    <t>sleep, health, recovery</t>
   </si>
   <si>
     <t>uk</t>
   </si>
   <si>
-    <t>Travel Tips for Exploring Europe</t>
+    <t>How to Organize Your Home Efficiently</t>
   </si>
   <si>
-    <t>travel, europe, tips, tourism</t>
+    <t>organization, home, minimalism</t>
   </si>
   <si>
     <t>es</t>
   </si>
   <si>
-    <t>How to Start Learning Programming</t>
+    <t>How to Learn a New Language Faster</t>
   </si>
   <si>
-    <t>programming, coding, beginner guide</t>
+    <t>language learning, tips</t>
   </si>
   <si>
     <t>zh</t>
   </si>
   <si>
-    <t>The Benefits of Minimalist Living</t>
+    <t>How to Travel on a Budget</t>
   </si>
   <si>
-    <t>minimalism, lifestyle, declutter</t>
+    <t>travel, budget, tips</t>
+  </si>
+  <si>
+    <t>hi</t>
+  </si>
+  <si>
+    <t>The Perfect Morning Routine</t>
+  </si>
+  <si>
+    <t>routine, health, habits</t>
   </si>
   <si>
     <t>ar</t>
   </si>
   <si>
-    <t>Best Time Management Techniques</t>
+    <t>Why Everyone Is Burned Out Today</t>
   </si>
   <si>
-    <t>time management, productivity, focus</t>
+    <t>burnout, stress, work</t>
   </si>
   <si>
-    <t>Using AI for SEO Content Generation</t>
+    <t>Are You Addicted to Your Phone?</t>
   </si>
   <si>
-    <t>SEO, AI content, keywords, ranking</t>
+    <t>addiction, smartphones, dopamine</t>
   </si>
   <si>
-    <t>Why You Keep Procrastinating (And How to Stop)</t>
+    <t>Why People Are Rejecting Consumerism</t>
   </si>
   <si>
-    <t>procrastination, psychology, productivity, habits</t>
+    <t>minimalism, lifestyle</t>
   </si>
   <si>
-    <t>The Hidden Dangers of Social Media</t>
+    <t>Why the 9–5 Job Is a Trap</t>
   </si>
   <si>
-    <t>social media, mental health, addiction, dopamine</t>
+    <t>jobs, career, freedom</t>
   </si>
   <si>
-    <t>Which Jobs Will AI Replace First?</t>
+    <t>Is College Becoming Useless?</t>
   </si>
   <si>
-    <t>AI jobs, automation, future work, technology</t>
+    <t>education, college, career</t>
   </si>
   <si>
-    <t>What It's Really Like to Live in Spain</t>
+    <t>How to Protect Your Data Online</t>
   </si>
   <si>
-    <t>Spain, expat life, cost of living, lifestyle</t>
+    <t>cybersecurity, privacy, data protection</t>
   </si>
   <si>
-    <t>10 Business Ideas You Can Start with $0</t>
+    <t>What Smartphones Will Look Like in 2030</t>
   </si>
   <si>
-    <t>business ideas, startup, no money, entrepreneurship</t>
+    <t>smartphones, future tech</t>
+  </si>
+  <si>
+    <t>Best Alternatives to ChatGPT</t>
+  </si>
+  <si>
+    <t>AI tools, chatbots, alternatives</t>
+  </si>
+  <si>
+    <t>How AI Is Already Changing Your Daily Life</t>
+  </si>
+  <si>
+    <t>AI tools, everyday AI, automation</t>
+  </si>
+  <si>
+    <t>How Students Use AI to Learn Faster</t>
+  </si>
+  <si>
+    <t>AI education, students, productivity</t>
+  </si>
+  <si>
+    <t>How to Avoid Online Scams in 2026</t>
+  </si>
+  <si>
+    <t>scams, online safety, fraud</t>
+  </si>
+  <si>
+    <t>How to Earn Money Selling Digital Products</t>
+  </si>
+  <si>
+    <t>digital products, passive income</t>
+  </si>
+  <si>
+    <t>7 Reasons Why People Stay Poor</t>
+  </si>
+  <si>
+    <t>poverty, money habits, finance</t>
+  </si>
+  <si>
+    <t>Best Side Hustles That Actually Work in 2026</t>
+  </si>
+  <si>
+    <t>side hustle, online income, money</t>
+  </si>
+  <si>
+    <t>How Ordinary People Become Rich</t>
+  </si>
+  <si>
+    <t>wealth, money, success, mindset</t>
+  </si>
+  <si>
+    <t>How to Build Real Confidence</t>
+  </si>
+  <si>
+    <t>confidence, self esteem, psychology</t>
+  </si>
+  <si>
+    <t>How to Stop Overthinking Everything</t>
+  </si>
+  <si>
+    <t>overthinking, anxiety, mental health</t>
+  </si>
+  <si>
+    <t>Why Motivation Doesn’t Work</t>
+  </si>
+  <si>
+    <t>motivation, discipline, habits</t>
   </si>
   <si>
     <t>Signs You're in a Toxic Relationship</t>
@@ -171,82 +234,16 @@
     <t>relationships, toxic people, psychology</t>
   </si>
   <si>
-    <t>Why Motivation Doesn’t Work</t>
+    <t>Why Fear of Failure Is Holding You Back</t>
   </si>
   <si>
-    <t>motivation, discipline, habits</t>
+    <t>fear, psychology, self growth, mindset</t>
   </si>
   <si>
-    <t>How to Stop Overthinking Everything</t>
+    <t>10 Business Ideas You Can Start with $0</t>
   </si>
   <si>
-    <t>overthinking, anxiety, mental health</t>
-  </si>
-  <si>
-    <t>How to Build Real Confidence</t>
-  </si>
-  <si>
-    <t>confidence, self esteem, psychology</t>
-  </si>
-  <si>
-    <t>Best Side Hustles That Actually Work in 2026</t>
-  </si>
-  <si>
-    <t>side hustle, online income, money</t>
-  </si>
-  <si>
-    <t>7 Reasons Why People Stay Poor</t>
-  </si>
-  <si>
-    <t>poverty, money habits, finance</t>
-  </si>
-  <si>
-    <t>How to Earn Money Selling Digital Products</t>
-  </si>
-  <si>
-    <t>digital products, passive income</t>
-  </si>
-  <si>
-    <t>How to Avoid Online Scams in 2026</t>
-  </si>
-  <si>
-    <t>scams, online safety, fraud</t>
-  </si>
-  <si>
-    <t>Is College Becoming Useless?</t>
-  </si>
-  <si>
-    <t>education, college, career</t>
-  </si>
-  <si>
-    <t>Why the 9–5 Job Is a Trap</t>
-  </si>
-  <si>
-    <t>jobs, career, freedom</t>
-  </si>
-  <si>
-    <t>Why People Are Rejecting Consumerism</t>
-  </si>
-  <si>
-    <t>minimalism, lifestyle</t>
-  </si>
-  <si>
-    <t>Are You Addicted to Your Phone?</t>
-  </si>
-  <si>
-    <t>addiction, smartphones, dopamine</t>
-  </si>
-  <si>
-    <t>Why Everyone Is Burned Out Today</t>
-  </si>
-  <si>
-    <t>burnout, stress, work</t>
-  </si>
-  <si>
-    <t>How to Learn a New Language Faster</t>
-  </si>
-  <si>
-    <t>language learning, tips</t>
+    <t>business ideas, startup, no money, entrepreneurship</t>
   </si>
 </sst>
 </file>
@@ -626,7 +623,7 @@
         <v>13</v>
       </c>
       <c r="H2" s="6">
-        <v>46125.76736111111</v>
+        <v>46125.5</v>
       </c>
       <c r="I2" s="4" t="s">
         <v>14</v>
@@ -655,27 +652,27 @@
         <v>13</v>
       </c>
       <c r="H3" s="6">
-        <v>46125.768055555556</v>
+        <v>46125.666666666664</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="2">
-        <v>-1.003987878441E12</v>
+        <v>-1.003604311448E12</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="E4" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>12</v>
@@ -684,27 +681,27 @@
         <v>13</v>
       </c>
       <c r="H4" s="6">
-        <v>46125.76875</v>
+        <v>46125.854166666664</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="2">
-        <v>-1.003905847191E12</v>
+        <v>-1.003778564964E12</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E5" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>12</v>
@@ -713,7 +710,7 @@
         <v>13</v>
       </c>
       <c r="H5" s="6">
-        <v>46125.76944444444</v>
+        <v>46126.5</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>14</v>
@@ -721,16 +718,16 @@
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="2">
-        <v>-1.003958929517E12</v>
+        <v>-1.003604311448E12</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E6" s="4" t="b">
         <v>0</v>
@@ -742,7 +739,7 @@
         <v>13</v>
       </c>
       <c r="H6" s="6">
-        <v>46125.768055555556</v>
+        <v>46126.666666666664</v>
       </c>
       <c r="I6" s="4" t="s">
         <v>14</v>
@@ -750,19 +747,19 @@
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="2">
-        <v>-1.003604311448E12</v>
+        <v>-1.003778564964E12</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E7" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>12</v>
@@ -771,27 +768,27 @@
         <v>13</v>
       </c>
       <c r="H7" s="6">
-        <v>46125.76736111111</v>
+        <v>46126.854166666664</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="2">
-        <v>-1.003778564964E12</v>
+        <v>-1.003604311448E12</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E8" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>12</v>
@@ -800,7 +797,7 @@
         <v>13</v>
       </c>
       <c r="H8" s="6">
-        <v>46125.771527777775</v>
+        <v>46127.5</v>
       </c>
       <c r="I8" s="4" t="s">
         <v>14</v>
@@ -808,16 +805,16 @@
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="2">
-        <v>-1.003987878441E12</v>
+        <v>-1.003778564964E12</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="E9" s="4" t="b">
         <v>0</v>
@@ -829,24 +826,24 @@
         <v>13</v>
       </c>
       <c r="H9" s="6">
-        <v>46125.768055555556</v>
+        <v>46127.666666666664</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="2">
-        <v>-1.003905847191E12</v>
+        <v>-1.003604311448E12</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E10" s="4" t="b">
         <v>0</v>
@@ -858,7 +855,7 @@
         <v>13</v>
       </c>
       <c r="H10" s="6">
-        <v>46125.76736111111</v>
+        <v>46127.854166666664</v>
       </c>
       <c r="I10" s="4" t="s">
         <v>14</v>
@@ -866,16 +863,16 @@
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="2">
-        <v>-1.003958929517E12</v>
+        <v>-1.003778564964E12</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E11" s="4" t="b">
         <v>0</v>
@@ -887,10 +884,10 @@
         <v>13</v>
       </c>
       <c r="H11" s="6">
-        <v>46125.77361111111</v>
+        <v>46128.5</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
@@ -898,13 +895,13 @@
         <v>-1.003604311448E12</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="E12" s="4" t="b">
         <v>0</v>
@@ -916,7 +913,7 @@
         <v>13</v>
       </c>
       <c r="H12" s="6">
-        <v>46125.768055555556</v>
+        <v>46128.666666666664</v>
       </c>
       <c r="I12" s="4" t="s">
         <v>14</v>
@@ -927,16 +924,16 @@
         <v>-1.003778564964E12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="E13" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>12</v>
@@ -945,27 +942,27 @@
         <v>13</v>
       </c>
       <c r="H13" s="6">
-        <v>46125.775</v>
+        <v>46128.854166666664</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="2">
-        <v>-1.003987878441E12</v>
+        <v>-1.003604311448E12</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E14" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>12</v>
@@ -974,7 +971,7 @@
         <v>13</v>
       </c>
       <c r="H14" s="6">
-        <v>46125.768055555556</v>
+        <v>46129.5</v>
       </c>
       <c r="I14" s="4" t="s">
         <v>14</v>
@@ -982,19 +979,19 @@
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="2">
-        <v>-1.003905847191E12</v>
+        <v>-1.003778564964E12</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E15" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>12</v>
@@ -1003,24 +1000,24 @@
         <v>13</v>
       </c>
       <c r="H15" s="6">
-        <v>46125.76736111111</v>
+        <v>46129.666666666664</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="2">
-        <v>-1.003958929517E12</v>
+        <v>-1.003604311448E12</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="E16" s="4" t="b">
         <v>0</v>
@@ -1032,24 +1029,24 @@
         <v>13</v>
       </c>
       <c r="H16" s="6">
-        <v>46125.76736111111</v>
+        <v>46129.854166666664</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="2">
-        <v>-1.003604311448E12</v>
+        <v>-1.003778564964E12</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="E17" s="4" t="b">
         <v>0</v>
@@ -1061,7 +1058,7 @@
         <v>13</v>
       </c>
       <c r="H17" s="6">
-        <v>46125.77777777778</v>
+        <v>46130.5</v>
       </c>
       <c r="I17" s="4" t="s">
         <v>14</v>
@@ -1069,16 +1066,16 @@
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="2">
-        <v>-1.003778564964E12</v>
+        <v>-1.003604311448E12</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="E18" s="4" t="b">
         <v>0</v>
@@ -1090,7 +1087,7 @@
         <v>13</v>
       </c>
       <c r="H18" s="6">
-        <v>46125.768055555556</v>
+        <v>46130.666666666664</v>
       </c>
       <c r="I18" s="4" t="s">
         <v>14</v>
@@ -1098,19 +1095,19 @@
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="2">
-        <v>-1.003987878441E12</v>
+        <v>-1.003778564964E12</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E19" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>12</v>
@@ -1119,24 +1116,24 @@
         <v>13</v>
       </c>
       <c r="H19" s="6">
-        <v>46125.77916666667</v>
+        <v>46130.854166666664</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="2">
-        <v>-1.003905847191E12</v>
+        <v>-1.003604311448E12</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="E20" s="4" t="b">
         <v>0</v>
@@ -1148,7 +1145,7 @@
         <v>13</v>
       </c>
       <c r="H20" s="6">
-        <v>46125.76736111111</v>
+        <v>46131.5</v>
       </c>
       <c r="I20" s="4" t="s">
         <v>14</v>
@@ -1156,16 +1153,16 @@
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="2">
-        <v>-1.003958929517E12</v>
+        <v>-1.003778564964E12</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="E21" s="4" t="b">
         <v>0</v>
@@ -1177,10 +1174,10 @@
         <v>13</v>
       </c>
       <c r="H21" s="6">
-        <v>46125.768055555556</v>
+        <v>46131.666666666664</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
@@ -1188,16 +1185,16 @@
         <v>-1.003604311448E12</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="E22" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>12</v>
@@ -1206,7 +1203,7 @@
         <v>13</v>
       </c>
       <c r="H22" s="6">
-        <v>46125.78125</v>
+        <v>46131.854166666664</v>
       </c>
       <c r="I22" s="4" t="s">
         <v>14</v>
@@ -1217,16 +1214,16 @@
         <v>-1.003778564964E12</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="E23" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>12</v>
@@ -1235,7 +1232,7 @@
         <v>13</v>
       </c>
       <c r="H23" s="6">
-        <v>46125.76736111111</v>
+        <v>46132.5</v>
       </c>
       <c r="I23" s="4" t="s">
         <v>14</v>
@@ -1243,16 +1240,16 @@
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="2">
-        <v>-1.003987878441E12</v>
+        <v>-1.003604311448E12</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E24" s="4" t="b">
         <v>0</v>
@@ -1264,7 +1261,7 @@
         <v>13</v>
       </c>
       <c r="H24" s="6">
-        <v>46125.768055555556</v>
+        <v>46132.666666666664</v>
       </c>
       <c r="I24" s="4" t="s">
         <v>14</v>
@@ -1272,19 +1269,19 @@
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="2">
-        <v>-1.003905847191E12</v>
+        <v>-1.003778564964E12</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="E25" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>12</v>
@@ -1293,24 +1290,24 @@
         <v>13</v>
       </c>
       <c r="H25" s="6">
-        <v>46125.76736111111</v>
+        <v>46132.854166666664</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="2">
-        <v>-1.003958929517E12</v>
+        <v>-1.003604311448E12</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E26" s="4" t="b">
         <v>0</v>
@@ -1322,7 +1319,7 @@
         <v>13</v>
       </c>
       <c r="H26" s="6">
-        <v>46125.768055555556</v>
+        <v>46133.5</v>
       </c>
       <c r="I26" s="4" t="s">
         <v>14</v>
@@ -1330,16 +1327,16 @@
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="2">
-        <v>-1.003604311448E12</v>
+        <v>-1.003778564964E12</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E27" s="4" t="b">
         <v>0</v>
@@ -1351,24 +1348,24 @@
         <v>13</v>
       </c>
       <c r="H27" s="6">
-        <v>46125.76736111111</v>
+        <v>46133.666666666664</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="2">
-        <v>-1.003778564964E12</v>
+        <v>-1.003604311448E12</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="E28" s="4" t="b">
         <v>1</v>
@@ -1380,27 +1377,27 @@
         <v>13</v>
       </c>
       <c r="H28" s="6">
-        <v>46125.768055555556</v>
+        <v>46133.854166666664</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="2">
-        <v>-1.003987878441E12</v>
+        <v>-1.003778564964E12</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="E29" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>12</v>
@@ -1409,156 +1406,66 @@
         <v>13</v>
       </c>
       <c r="H29" s="6">
-        <v>46125.768055555556</v>
+        <v>46134.854166666664</v>
       </c>
       <c r="I29" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="2">
-        <v>-1.003905847191E12</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E30" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G30" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H30" s="6">
-        <v>46125.78680555556</v>
-      </c>
-      <c r="I30" s="4" t="s">
-        <v>14</v>
-      </c>
+      <c r="A30" s="7"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="7"/>
+      <c r="H30" s="7"/>
+      <c r="I30" s="7"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="2">
-        <v>-1.003604311448E12</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E31" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G31" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H31" s="6">
-        <v>46125.7875</v>
-      </c>
-      <c r="I31" s="4" t="s">
-        <v>14</v>
-      </c>
+      <c r="A31" s="7"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="7"/>
+      <c r="H31" s="7"/>
+      <c r="I31" s="7"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="2">
-        <v>-1.003778564964E12</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E32" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G32" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H32" s="6">
-        <v>46125.76736111111</v>
-      </c>
-      <c r="I32" s="4" t="s">
-        <v>20</v>
-      </c>
+      <c r="A32" s="7"/>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+      <c r="G32" s="7"/>
+      <c r="H32" s="7"/>
+      <c r="I32" s="7"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="2">
-        <v>-1.003987878441E12</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E33" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G33" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H33" s="6">
-        <v>46125.78888888889</v>
-      </c>
-      <c r="I33" s="4" t="s">
-        <v>14</v>
-      </c>
+      <c r="A33" s="7"/>
+      <c r="B33" s="7"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="7"/>
+      <c r="H33" s="7"/>
+      <c r="I33" s="7"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="2">
-        <v>-1.003905847191E12</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E34" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G34" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H34" s="6">
-        <v>46125.76736111111</v>
-      </c>
-      <c r="I34" s="4" t="s">
-        <v>14</v>
-      </c>
+      <c r="A34" s="7"/>
+      <c r="B34" s="7"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="7"/>
+      <c r="H34" s="7"/>
+      <c r="I34" s="7"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="7"/>
@@ -3288,59 +3195,59 @@
       <c r="I191" s="7"/>
     </row>
     <row r="192" ht="15.75" customHeight="1">
-      <c r="A192" s="7"/>
-      <c r="B192" s="7"/>
-      <c r="C192" s="7"/>
-      <c r="D192" s="7"/>
-      <c r="E192" s="7"/>
-      <c r="F192" s="7"/>
-      <c r="G192" s="7"/>
-      <c r="H192" s="7"/>
-      <c r="I192" s="7"/>
+      <c r="A192" s="8"/>
+      <c r="B192" s="8"/>
+      <c r="C192" s="8"/>
+      <c r="D192" s="8"/>
+      <c r="E192" s="8"/>
+      <c r="F192" s="8"/>
+      <c r="G192" s="8"/>
+      <c r="H192" s="8"/>
+      <c r="I192" s="8"/>
     </row>
     <row r="193" ht="15.75" customHeight="1">
-      <c r="A193" s="7"/>
-      <c r="B193" s="7"/>
-      <c r="C193" s="7"/>
-      <c r="D193" s="7"/>
-      <c r="E193" s="7"/>
-      <c r="F193" s="7"/>
-      <c r="G193" s="7"/>
-      <c r="H193" s="7"/>
-      <c r="I193" s="7"/>
+      <c r="A193" s="8"/>
+      <c r="B193" s="8"/>
+      <c r="C193" s="8"/>
+      <c r="D193" s="8"/>
+      <c r="E193" s="8"/>
+      <c r="F193" s="8"/>
+      <c r="G193" s="8"/>
+      <c r="H193" s="8"/>
+      <c r="I193" s="8"/>
     </row>
     <row r="194" ht="15.75" customHeight="1">
-      <c r="A194" s="7"/>
-      <c r="B194" s="7"/>
-      <c r="C194" s="7"/>
-      <c r="D194" s="7"/>
-      <c r="E194" s="7"/>
-      <c r="F194" s="7"/>
-      <c r="G194" s="7"/>
-      <c r="H194" s="7"/>
-      <c r="I194" s="7"/>
+      <c r="A194" s="8"/>
+      <c r="B194" s="8"/>
+      <c r="C194" s="8"/>
+      <c r="D194" s="8"/>
+      <c r="E194" s="8"/>
+      <c r="F194" s="8"/>
+      <c r="G194" s="8"/>
+      <c r="H194" s="8"/>
+      <c r="I194" s="8"/>
     </row>
     <row r="195" ht="15.75" customHeight="1">
-      <c r="A195" s="7"/>
-      <c r="B195" s="7"/>
-      <c r="C195" s="7"/>
-      <c r="D195" s="7"/>
-      <c r="E195" s="7"/>
-      <c r="F195" s="7"/>
-      <c r="G195" s="7"/>
-      <c r="H195" s="7"/>
-      <c r="I195" s="7"/>
+      <c r="A195" s="8"/>
+      <c r="B195" s="8"/>
+      <c r="C195" s="8"/>
+      <c r="D195" s="8"/>
+      <c r="E195" s="8"/>
+      <c r="F195" s="8"/>
+      <c r="G195" s="8"/>
+      <c r="H195" s="8"/>
+      <c r="I195" s="8"/>
     </row>
     <row r="196" ht="15.75" customHeight="1">
-      <c r="A196" s="7"/>
-      <c r="B196" s="7"/>
-      <c r="C196" s="7"/>
-      <c r="D196" s="7"/>
-      <c r="E196" s="7"/>
-      <c r="F196" s="7"/>
-      <c r="G196" s="7"/>
-      <c r="H196" s="7"/>
-      <c r="I196" s="7"/>
+      <c r="A196" s="8"/>
+      <c r="B196" s="8"/>
+      <c r="C196" s="8"/>
+      <c r="D196" s="8"/>
+      <c r="E196" s="8"/>
+      <c r="F196" s="8"/>
+      <c r="G196" s="8"/>
+      <c r="H196" s="8"/>
+      <c r="I196" s="8"/>
     </row>
     <row r="197" ht="15.75" customHeight="1">
       <c r="A197" s="8"/>
@@ -10196,13 +10103,13 @@
       <c r="I819" s="8"/>
     </row>
     <row r="820" ht="15.75" customHeight="1">
-      <c r="A820" s="8"/>
-      <c r="B820" s="8"/>
-      <c r="C820" s="8"/>
-      <c r="D820" s="8"/>
-      <c r="E820" s="8"/>
-      <c r="F820" s="8"/>
-      <c r="G820" s="8"/>
+      <c r="A820" s="7"/>
+      <c r="B820" s="7"/>
+      <c r="C820" s="7"/>
+      <c r="D820" s="7"/>
+      <c r="E820" s="7"/>
+      <c r="F820" s="7"/>
+      <c r="G820" s="7"/>
       <c r="H820" s="8"/>
       <c r="I820" s="8"/>
     </row>
@@ -10251,13 +10158,13 @@
       <c r="I824" s="8"/>
     </row>
     <row r="825" ht="15.75" customHeight="1">
-      <c r="A825" s="7"/>
-      <c r="B825" s="7"/>
-      <c r="C825" s="7"/>
-      <c r="D825" s="7"/>
-      <c r="E825" s="7"/>
-      <c r="F825" s="7"/>
-      <c r="G825" s="7"/>
+      <c r="A825" s="8"/>
+      <c r="B825" s="8"/>
+      <c r="C825" s="8"/>
+      <c r="D825" s="8"/>
+      <c r="E825" s="8"/>
+      <c r="F825" s="8"/>
+      <c r="G825" s="8"/>
       <c r="H825" s="8"/>
       <c r="I825" s="8"/>
     </row>
@@ -11867,70 +11774,15 @@
       <c r="H971" s="8"/>
       <c r="I971" s="8"/>
     </row>
-    <row r="972" ht="15.75" customHeight="1">
-      <c r="A972" s="8"/>
-      <c r="B972" s="8"/>
-      <c r="C972" s="8"/>
-      <c r="D972" s="8"/>
-      <c r="E972" s="8"/>
-      <c r="F972" s="8"/>
-      <c r="G972" s="8"/>
-      <c r="H972" s="8"/>
-      <c r="I972" s="8"/>
-    </row>
-    <row r="973" ht="15.75" customHeight="1">
-      <c r="A973" s="8"/>
-      <c r="B973" s="8"/>
-      <c r="C973" s="8"/>
-      <c r="D973" s="8"/>
-      <c r="E973" s="8"/>
-      <c r="F973" s="8"/>
-      <c r="G973" s="8"/>
-      <c r="H973" s="8"/>
-      <c r="I973" s="8"/>
-    </row>
-    <row r="974" ht="15.75" customHeight="1">
-      <c r="A974" s="8"/>
-      <c r="B974" s="8"/>
-      <c r="C974" s="8"/>
-      <c r="D974" s="8"/>
-      <c r="E974" s="8"/>
-      <c r="F974" s="8"/>
-      <c r="G974" s="8"/>
-      <c r="H974" s="8"/>
-      <c r="I974" s="8"/>
-    </row>
-    <row r="975" ht="15.75" customHeight="1">
-      <c r="A975" s="8"/>
-      <c r="B975" s="8"/>
-      <c r="C975" s="8"/>
-      <c r="D975" s="8"/>
-      <c r="E975" s="8"/>
-      <c r="F975" s="8"/>
-      <c r="G975" s="8"/>
-      <c r="H975" s="8"/>
-      <c r="I975" s="8"/>
-    </row>
-    <row r="976" ht="15.75" customHeight="1">
-      <c r="A976" s="8"/>
-      <c r="B976" s="8"/>
-      <c r="C976" s="8"/>
-      <c r="D976" s="8"/>
-      <c r="E976" s="8"/>
-      <c r="F976" s="8"/>
-      <c r="G976" s="8"/>
-      <c r="H976" s="8"/>
-      <c r="I976" s="8"/>
-    </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I2:I975">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I2:I970">
       <formula1>"instant,approval"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E2:E975">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E2:E970">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D2:D975">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D2:D970">
       <formula1>"en,ru,uk,es,zh,hi,ar"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11963,12 +11815,7 @@
     <hyperlink r:id="rId26" ref="G27"/>
     <hyperlink r:id="rId27" ref="G28"/>
     <hyperlink r:id="rId28" ref="G29"/>
-    <hyperlink r:id="rId29" ref="G30"/>
-    <hyperlink r:id="rId30" ref="G31"/>
-    <hyperlink r:id="rId31" ref="G32"/>
-    <hyperlink r:id="rId32" ref="G33"/>
-    <hyperlink r:id="rId33" ref="G34"/>
   </hyperlinks>
-  <drawing r:id="rId34"/>
+  <drawing r:id="rId29"/>
 </worksheet>
 </file>